--- a/Clara_Comparison.xlsx
+++ b/Clara_Comparison.xlsx
@@ -75,11 +75,11 @@
   </si>
   <si>
     <t>Exp
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>Exp
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>DB
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t>DB
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>DB
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>Match</t>
@@ -127,7 +127,7 @@
     <t>X</t>
   </si>
   <si>
-    <t>NO</t>
+    <t>NC</t>
   </si>
   <si>
     <t>T</t>
@@ -172,7 +172,7 @@
     <t>EM - 212</t>
   </si>
   <si>
-    <t>NC</t>
+    <t>NO</t>
   </si>
   <si>
     <t>AV220-1</t>
